--- a/Min_Diagramportal/data_pipeline/Prognoser_Manad.xlsx
+++ b/Min_Diagramportal/data_pipeline/Prognoser_Manad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EF69C2-8567-4731-80F9-068D8A0C9E05}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BED7034-9F1F-4498-9791-1B0904D6347E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{667748E1-8596-4103-B17E-56D7005BF702}"/>
   </bookViews>
@@ -2934,6 +2934,24 @@
       <c r="B74">
         <v>1</v>
       </c>
+      <c r="C74">
+        <v>710</v>
+      </c>
+      <c r="D74">
+        <v>1510</v>
+      </c>
+      <c r="E74">
+        <v>1290</v>
+      </c>
+      <c r="F74">
+        <v>9940</v>
+      </c>
+      <c r="H74">
+        <v>9450</v>
+      </c>
+      <c r="J74">
+        <v>169420</v>
+      </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">

--- a/Min_Diagramportal/data_pipeline/Prognoser_Manad.xlsx
+++ b/Min_Diagramportal/data_pipeline/Prognoser_Manad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BED7034-9F1F-4498-9791-1B0904D6347E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F400DA6C-7AFC-4AF9-ABC2-3EB74FC51665}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{667748E1-8596-4103-B17E-56D7005BF702}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="39">
   <si>
     <t>Befolkningsförändring_Prognos</t>
   </si>
@@ -2946,8 +2946,14 @@
       <c r="F74">
         <v>9940</v>
       </c>
+      <c r="G74" t="s">
+        <v>7</v>
+      </c>
       <c r="H74">
         <v>9450</v>
+      </c>
+      <c r="I74" t="s">
+        <v>7</v>
       </c>
       <c r="J74">
         <v>169420</v>
@@ -2960,6 +2966,30 @@
       <c r="B75">
         <v>2</v>
       </c>
+      <c r="C75">
+        <v>710</v>
+      </c>
+      <c r="D75">
+        <v>1510</v>
+      </c>
+      <c r="E75">
+        <v>1290</v>
+      </c>
+      <c r="F75">
+        <v>9940</v>
+      </c>
+      <c r="G75" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75">
+        <v>9450</v>
+      </c>
+      <c r="I75" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75">
+        <v>169420</v>
+      </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
@@ -2968,6 +2998,30 @@
       <c r="B76">
         <v>3</v>
       </c>
+      <c r="C76">
+        <v>710</v>
+      </c>
+      <c r="D76">
+        <v>1510</v>
+      </c>
+      <c r="E76">
+        <v>1290</v>
+      </c>
+      <c r="F76">
+        <v>9940</v>
+      </c>
+      <c r="G76" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76">
+        <v>9450</v>
+      </c>
+      <c r="I76" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>169420</v>
+      </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
@@ -2976,6 +3030,30 @@
       <c r="B77">
         <v>4</v>
       </c>
+      <c r="C77">
+        <v>710</v>
+      </c>
+      <c r="D77">
+        <v>1510</v>
+      </c>
+      <c r="E77">
+        <v>1290</v>
+      </c>
+      <c r="F77">
+        <v>9940</v>
+      </c>
+      <c r="G77" t="s">
+        <v>7</v>
+      </c>
+      <c r="H77">
+        <v>9450</v>
+      </c>
+      <c r="I77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J77">
+        <v>169420</v>
+      </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
@@ -2984,6 +3062,30 @@
       <c r="B78">
         <v>5</v>
       </c>
+      <c r="C78">
+        <v>710</v>
+      </c>
+      <c r="D78">
+        <v>1510</v>
+      </c>
+      <c r="E78">
+        <v>1290</v>
+      </c>
+      <c r="F78">
+        <v>9940</v>
+      </c>
+      <c r="G78" t="s">
+        <v>7</v>
+      </c>
+      <c r="H78">
+        <v>9450</v>
+      </c>
+      <c r="I78" t="s">
+        <v>7</v>
+      </c>
+      <c r="J78">
+        <v>169420</v>
+      </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
@@ -2992,6 +3094,30 @@
       <c r="B79">
         <v>6</v>
       </c>
+      <c r="C79">
+        <v>710</v>
+      </c>
+      <c r="D79">
+        <v>1510</v>
+      </c>
+      <c r="E79">
+        <v>1290</v>
+      </c>
+      <c r="F79">
+        <v>9940</v>
+      </c>
+      <c r="G79" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79">
+        <v>9450</v>
+      </c>
+      <c r="I79" t="s">
+        <v>7</v>
+      </c>
+      <c r="J79">
+        <v>169420</v>
+      </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
@@ -3000,45 +3126,189 @@
       <c r="B80">
         <v>7</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <v>710</v>
+      </c>
+      <c r="D80">
+        <v>1510</v>
+      </c>
+      <c r="E80">
+        <v>1290</v>
+      </c>
+      <c r="F80">
+        <v>9940</v>
+      </c>
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <v>9450</v>
+      </c>
+      <c r="I80" t="s">
+        <v>7</v>
+      </c>
+      <c r="J80">
+        <v>169420</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2026</v>
       </c>
       <c r="B81">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <v>710</v>
+      </c>
+      <c r="D81">
+        <v>1510</v>
+      </c>
+      <c r="E81">
+        <v>1290</v>
+      </c>
+      <c r="F81">
+        <v>9940</v>
+      </c>
+      <c r="G81" t="s">
+        <v>7</v>
+      </c>
+      <c r="H81">
+        <v>9450</v>
+      </c>
+      <c r="I81" t="s">
+        <v>7</v>
+      </c>
+      <c r="J81">
+        <v>169420</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2026</v>
       </c>
       <c r="B82">
         <v>9</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <v>710</v>
+      </c>
+      <c r="D82">
+        <v>1510</v>
+      </c>
+      <c r="E82">
+        <v>1290</v>
+      </c>
+      <c r="F82">
+        <v>9940</v>
+      </c>
+      <c r="G82" t="s">
+        <v>7</v>
+      </c>
+      <c r="H82">
+        <v>9450</v>
+      </c>
+      <c r="I82" t="s">
+        <v>7</v>
+      </c>
+      <c r="J82">
+        <v>169420</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2026</v>
       </c>
       <c r="B83">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <v>710</v>
+      </c>
+      <c r="D83">
+        <v>1510</v>
+      </c>
+      <c r="E83">
+        <v>1290</v>
+      </c>
+      <c r="F83">
+        <v>9940</v>
+      </c>
+      <c r="G83" t="s">
+        <v>7</v>
+      </c>
+      <c r="H83">
+        <v>9450</v>
+      </c>
+      <c r="I83" t="s">
+        <v>7</v>
+      </c>
+      <c r="J83">
+        <v>169420</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2026</v>
       </c>
       <c r="B84">
         <v>11</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <v>710</v>
+      </c>
+      <c r="D84">
+        <v>1510</v>
+      </c>
+      <c r="E84">
+        <v>1290</v>
+      </c>
+      <c r="F84">
+        <v>9940</v>
+      </c>
+      <c r="G84" t="s">
+        <v>7</v>
+      </c>
+      <c r="H84">
+        <v>9450</v>
+      </c>
+      <c r="I84" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84">
+        <v>169420</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2026</v>
       </c>
       <c r="B85">
         <v>12</v>
+      </c>
+      <c r="C85">
+        <v>710</v>
+      </c>
+      <c r="D85">
+        <v>1510</v>
+      </c>
+      <c r="E85">
+        <v>1290</v>
+      </c>
+      <c r="F85">
+        <v>9940</v>
+      </c>
+      <c r="G85" t="s">
+        <v>7</v>
+      </c>
+      <c r="H85">
+        <v>9450</v>
+      </c>
+      <c r="I85" t="s">
+        <v>7</v>
+      </c>
+      <c r="J85">
+        <v>169420</v>
       </c>
     </row>
   </sheetData>
